--- a/out/MLP-Mamba1_repeat_4_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001422896106913686</v>
+        <v>-0.0001417218889738433</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1634634334454633</v>
+        <v>-0.1628112302331682</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1629529521221421</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.163728478709457</v>
+        <v>-0.1630752779334805</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4414011160822506</v>
+        <v>0.4398555022719452</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.719921774240363</v>
+        <v>0.7174807797606145</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03144977343234777</v>
+        <v>0.03133964877287428</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3407116348671105</v>
+        <v>0.339598484212921</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05515205867883088</v>
+        <v>0.0549590658675993</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4195557402121396</v>
+        <v>0.4181665084067071</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06700354967487197</v>
+        <v>0.06676846262842821</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.498405276471619</v>
+        <v>0.4967397625604092</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01773065301807129</v>
+        <v>0.01766860810848735</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4667778174220396</v>
+        <v>0.4652229765128137</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009850297868344071</v>
+        <v>0.009815811846692567</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4687307174036617</v>
+        <v>0.4671690253386351</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02069592587405106</v>
+        <v>0.02062350323120389</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.254026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5002863370902836</v>
+        <v>0.498614224441865</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008128570460896165</v>
+        <v>0.008099504693912615</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4958279611259461</v>
+        <v>0.4941714321281088</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005787332183912083</v>
+        <v>0.005766632962290003</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4992706660345695</v>
+        <v>0.4976023309501314</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002274899322861753</v>
+        <v>0.00226675197566868</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4980286244444985</v>
+        <v>0.4963643425121524</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001288245647120945</v>
+        <v>0.001285162820786926</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4983304303256155</v>
+        <v>0.4966652337279529</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004882350768863232</v>
+        <v>0.0004858863384249597</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4980160783410882</v>
+        <v>0.4963519873631957</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002262016931173962</v>
+        <v>0.00022510073267398</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4979798958025896</v>
+        <v>0.496315879815992</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4979130384761232</v>
+        <v>0.4962490224895256</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4978732724299645</v>
+        <v>0.4962092564433669</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4978682530692713</v>
+        <v>0.4962042370826737</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4978642350249277</v>
+        <v>0.49620021903833</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4978618003547369</v>
+        <v>0.4961977843681392</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4978562831127472</v>
+        <v>0.4961922671261495</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4978499591187392</v>
+        <v>0.4961859431321416</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4978445913301608</v>
+        <v>0.4961805753435632</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9612393007297437</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4978446280786525</v>
+        <v>0.4961806120920549</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4978447383241281</v>
+        <v>0.4961807223375305</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4978448118211117</v>
+        <v>0.4961807958345141</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4978449955635709</v>
+        <v>0.4961809795769733</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4978465390002274</v>
+        <v>0.4961825230136297</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4978480089399004</v>
+        <v>0.4961839929533028</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4978492583886224</v>
+        <v>0.4961852424020248</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4978506180828197</v>
+        <v>0.4961866020962221</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4978484131733105</v>
+        <v>0.4961843971867128</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4978480089399004</v>
+        <v>0.4961839929533028</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4978471637245885</v>
+        <v>0.4961831477379908</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4978477149519657</v>
+        <v>0.4961836989653681</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4978473842155393</v>
+        <v>0.4961833682289417</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4978470902276048</v>
+        <v>0.4961830742410072</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4978471637245885</v>
+        <v>0.4961831477379908</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4978467227426865</v>
+        <v>0.4961827067560889</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.497846612497211</v>
+        <v>0.4961825965106134</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4978465757487193</v>
+        <v>0.4961825597621217</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4978467227426865</v>
+        <v>0.4961827067560889</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4978462450122929</v>
+        <v>0.4961822290256953</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4978472004730802</v>
+        <v>0.4961831844864825</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4978471637245885</v>
+        <v>0.4961831477379908</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4978468329881621</v>
+        <v>0.4961828170015644</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.497847273970064</v>
+        <v>0.4961832579834664</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4978466492457029</v>
+        <v>0.4961826332591053</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4978464655032437</v>
+        <v>0.4961824495166461</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4978460612698337</v>
+        <v>0.4961820452832361</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4978452160545218</v>
+        <v>0.4961812000679241</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4978451793060301</v>
+        <v>0.4961811633194324</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4978453262999973</v>
+        <v>0.4961813103133996</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4978452528030137</v>
+        <v>0.496181236816416</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4978453262999973</v>
+        <v>0.4961813103133996</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4978453630484892</v>
+        <v>0.4961813470618916</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4978452528030137</v>
+        <v>0.496181236816416</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4978456937849156</v>
+        <v>0.496181677798318</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4978455835394401</v>
+        <v>0.4961815675528424</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4978455467909481</v>
+        <v>0.4961815308043505</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4978454732939645</v>
+        <v>0.4961814573073669</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4978454365454728</v>
+        <v>0.4961814205588752</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4978452160545218</v>
+        <v>0.4961812000679241</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4978451425575381</v>
+        <v>0.4961811265709405</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4978450690605545</v>
+        <v>0.4961810530739569</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4978451058090464</v>
+        <v>0.4961810898224488</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4978449955635709</v>
+        <v>0.4961809795769733</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4978451058090464</v>
+        <v>0.4961810898224488</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4978453997969809</v>
+        <v>0.4961813838103833</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.06038435250706128</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685288</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685288</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685288</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685286</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685286</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809756</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809756</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.3821290720809756</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809756</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001422896106913686</v>
+        <v>-0.0001132779036865104</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1634634334454633</v>
+        <v>-0.1301345543088539</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.3821290720809756</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809756</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1636057230561546</v>
+        <v>-0.1302478322125403</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.163728478709457</v>
+        <v>-0.1303475790395665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4414011160822506</v>
+        <v>0.3586666168363316</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.719921774240363</v>
+        <v>0.5876748221502295</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03144977343234777</v>
+        <v>0.02555492114540848</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3407116348671105</v>
+        <v>0.2795422660016271</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05515205867883088</v>
+        <v>0.04481462458786199</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4195557402121396</v>
+        <v>0.3436082495038004</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06700354967487197</v>
+        <v>0.05444478809562262</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.498405276471619</v>
+        <v>0.407678680308087</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01773065301807129</v>
+        <v>0.01440729004195258</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4667778174220396</v>
+        <v>0.3819792910988196</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009850297868344071</v>
+        <v>0.00800309447456406</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4687307174036617</v>
+        <v>0.3835652169372907</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02069592587405106</v>
+        <v>0.01681746221349067</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5002863370902836</v>
+        <v>0.4092062860254094</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008128570460896165</v>
+        <v>0.006603828767884212</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4958279611259461</v>
+        <v>0.4055827522795203</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005787332183912083</v>
+        <v>0.004700623048752878</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4992706660345695</v>
+        <v>0.408379141978991</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002274899322861753</v>
+        <v>0.001847163595225391</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4980286244444985</v>
+        <v>0.4073688163470463</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001288245647120945</v>
+        <v>0.001046243779900458</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4983304303256155</v>
+        <v>0.4076132447838616</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004882350768863232</v>
+        <v>0.0003954599076624671</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4980160783410882</v>
+        <v>0.407356712949601</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002262016931173962</v>
+        <v>0.0001832642358241654</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4979798958025896</v>
+        <v>0.4073263214539667</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.976915590716732e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4979130384761232</v>
+        <v>0.4072709524874641</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.980325908626812e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4978732724299645</v>
+        <v>0.4072374771351852</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4978682530692713</v>
+        <v>0.4072324614977024</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4978642350249277</v>
+        <v>0.40722826128838</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4978618003547369</v>
+        <v>0.4072252774092744</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4978562831127472</v>
+        <v>0.407219833664268</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4978499591187392</v>
+        <v>0.4072138409308377</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685302</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4978445913301608</v>
+        <v>0.4072084731422593</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809754</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4978446280786525</v>
+        <v>0.407208509890751</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809754</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4978447383241281</v>
+        <v>0.4072086201362266</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4978448118211117</v>
+        <v>0.4072086936332102</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4978449955635709</v>
+        <v>0.4072088773756693</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4978465390002274</v>
+        <v>0.4072104208123258</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4978480089399004</v>
+        <v>0.4072118907519989</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4978492583886224</v>
+        <v>0.4072131402007209</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809753</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4978506180828197</v>
+        <v>0.4072144998949182</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4978484131733105</v>
+        <v>0.4072122949854089</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4978480089399004</v>
+        <v>0.4072118907519989</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4978471637245885</v>
+        <v>0.4072110455366869</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4978477149519657</v>
+        <v>0.4072115967640642</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4978473842155393</v>
+        <v>0.4072112660276377</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4978470902276048</v>
+        <v>0.4072109720397033</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4978471637245885</v>
+        <v>0.4072110455366869</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4978467227426865</v>
+        <v>0.407210604554785</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.497846612497211</v>
+        <v>0.4072104943093094</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4978465757487193</v>
+        <v>0.4072104575608177</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809754</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4978467227426865</v>
+        <v>0.407210604554785</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809754</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4978462450122929</v>
+        <v>0.4072101268243913</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809753</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4978472004730802</v>
+        <v>0.4072110822851786</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685308</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4978471637245885</v>
+        <v>0.4072110455366869</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4978468329881621</v>
+        <v>0.4072107148002605</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.497847273970064</v>
+        <v>0.4072111557821624</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4978466492457029</v>
+        <v>0.4072105310578013</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4978464655032437</v>
+        <v>0.4072103473153422</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4978460612698337</v>
+        <v>0.4072099430819321</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4978452160545218</v>
+        <v>0.4072090978666202</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.2613603670668531</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4978451793060301</v>
+        <v>0.4072090611181285</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685302</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4978453262999973</v>
+        <v>0.4072092081120957</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4978452528030137</v>
+        <v>0.4072091346151121</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4978453262999973</v>
+        <v>0.4072092081120957</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4978453630484892</v>
+        <v>0.4072092448605876</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4978452528030137</v>
+        <v>0.4072091346151121</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4978456937849156</v>
+        <v>0.407209575597014</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4978455835394401</v>
+        <v>0.4072094653515385</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4978455467909481</v>
+        <v>0.4072094286030466</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4978454732939645</v>
+        <v>0.4072093551060629</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4978454365454728</v>
+        <v>0.4072093183575712</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4978452160545218</v>
+        <v>0.4072090978666202</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4978451425575381</v>
+        <v>0.4072090243696366</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4978450690605545</v>
+        <v>0.4072089508726529</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4978451058090464</v>
+        <v>0.4072089876211449</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809754</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4978449955635709</v>
+        <v>0.4072088773756693</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4978451058090464</v>
+        <v>0.4072089876211449</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4978453997969809</v>
+        <v>0.4072092816090793</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.487335592508316</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.06038435250706128</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5763806700706482</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.02000000000000024</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.8089956641197205</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4244112074375153</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.2863698601722717</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4089658558368683</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.529284656047821</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3387312591075897</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4804602861404419</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3658812642097473</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.6305188536643982</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.425559788942337</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5641407370567322</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.06136036706685288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4716542661190033</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5878766179084778</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.06136036706685288</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2251435965299606</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.06136036706685288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.3669618964195251</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.3664520978927612</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4178497493267059</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4846465885639191</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3209338784217834</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5522156953811646</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4110142290592194</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6682514548301697</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.06136036706685286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.271839439868927</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5123685002326965</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.06136036706685286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3596826493740082</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5459935665130615</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5819368362426758</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.6290298700332642</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.8920792937278748</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.1295353472232819</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.6312865018844604</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3821290720809756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.6151354908943176</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3821290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.2340506613254547</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3821290720809756</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7506064176559448</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.3473937511444092</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4673988521099091</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.7639381885528564</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3821290720809756</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6081134080886841</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7350853681564331</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.225618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.7723495960235596</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9629709124565125</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.225618511228804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7116767168045044</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001132779036865104</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1301345543088539</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.0187511146068573</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5821290720809756</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.8443449139595032</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.116000697016716</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4722023010253906</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.2394385784864426</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5680809617042542</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.30992591381073</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3821290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.7437095046043396</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2613603670668529</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4613057971000671</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6065155267715454</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5821290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5229589939117432</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.225618511228804</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.5420253276824951</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7493987679481506</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.225618511228804</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1302478322125403</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9410029053688049</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1303475790395665</v>
+        <v>-0.1302921591422821</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3586666168363316</v>
+        <v>0.3585212983285851</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.1083724573254585</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5876748221502295</v>
+        <v>0.5874393260151648</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02555492114540848</v>
+        <v>0.02554460381850764</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.8034417629241943</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2795422660016271</v>
+        <v>0.2794316134925867</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04481462458786199</v>
+        <v>0.04479640319212071</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.902105450630188</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3821290720809755</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3436082495038004</v>
+        <v>0.3434715481702604</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05444478809562262</v>
+        <v>0.05442233946519297</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.2057590484619141</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.407678680308087</v>
+        <v>0.4075159289919187</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01440729004195258</v>
+        <v>0.01440167959800084</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3622594773769379</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3819792910988196</v>
+        <v>0.3818268414356588</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00800309447456406</v>
+        <v>0.007999792621427214</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9897425770759583</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3835652169372907</v>
+        <v>0.3834121113124043</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01681746221349067</v>
+        <v>0.01680975767701757</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.6065806150436401</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4092062860254094</v>
+        <v>0.4090426094816876</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006603828767884212</v>
+        <v>0.006601406620635582</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.904570996761322</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4055827522795203</v>
+        <v>0.4054204019347159</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004700623048752878</v>
+        <v>0.004698898113617705</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.1606208682060242</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5821290720809755</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.408379141978991</v>
+        <v>0.408215764920396</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.7776421904563904</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4073688163470463</v>
+        <v>0.4072058067733696</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.1298214048147202</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4076132447838616</v>
+        <v>0.407450051467726</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2007837444543839</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.407356712949601</v>
+        <v>0.4071938871183836</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001832642358241654</v>
+        <v>0.0001821632753807493</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.09500638395547867</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4073263214539667</v>
+        <v>0.4071635706140441</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1100866347551346</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4072709524874641</v>
+        <v>0.4071082016475415</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4502686560153961</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4072374771351852</v>
+        <v>0.4070747262952626</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4526973068714142</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4072324614977024</v>
+        <v>0.4070697106577798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.7227317094802856</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.40722826128838</v>
+        <v>0.4070655104484575</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2645333707332611</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.06136036706685299</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4072252774092744</v>
+        <v>0.4070625265693518</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.0961652547121048</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7048498062146814</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.407219833664268</v>
+        <v>0.4070570828243454</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2200800031423569</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4072138409308377</v>
+        <v>0.4070510900909151</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5243516564369202</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.06136036706685302</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4072084731422593</v>
+        <v>0.4070457223023367</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4856862723827362</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5821290720809754</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.407208509890751</v>
+        <v>0.4070457590508284</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.6130328774452209</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5821290720809754</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4072086201362266</v>
+        <v>0.4070458692963039</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5479590892791748</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.225618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4072086936332102</v>
+        <v>0.4070459427932876</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.9842830896377563</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.225618511228804</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4072088773756693</v>
+        <v>0.4070461265357467</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.9803651571273804</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.225618511228804</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4072104208123258</v>
+        <v>0.4070476699724032</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.9562678337097168</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.225618511228804</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4072118907519989</v>
+        <v>0.4070491399120763</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.9781620502471924</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4072131402007209</v>
+        <v>0.4070503893607983</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9582897424697876</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5821290720809753</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4072144998949182</v>
+        <v>0.4070517490549956</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.001253647729754448</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4072122949854089</v>
+        <v>0.4070495441454863</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.02291245944797993</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4072118907519989</v>
+        <v>0.4070491399120763</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.8272796273231506</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4072110455366869</v>
+        <v>0.4070482946967643</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.06978026777505875</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4072115967640642</v>
+        <v>0.4070488459241416</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.06911052763462067</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4072112660276377</v>
+        <v>0.4070485151877152</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6126617789268494</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4072109720397033</v>
+        <v>0.4070482211997807</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.01362281572073698</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4072110455366869</v>
+        <v>0.4070482946967643</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3948512375354767</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.407210604554785</v>
+        <v>0.4070478537148624</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2108446508646011</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4072104943093094</v>
+        <v>0.4070477434693868</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.5269074440002441</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2613603670668531</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4072104575608177</v>
+        <v>0.4070477067208951</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.02062398195266724</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5821290720809754</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.407210604554785</v>
+        <v>0.4070478537148624</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.997871994972229</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5821290720809754</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4072101268243913</v>
+        <v>0.4070473759844687</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.8388389348983765</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5821290720809753</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4072110822851786</v>
+        <v>0.407048331445256</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.0439877100288868</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.06136036706685308</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4072110455366869</v>
+        <v>0.4070482946967643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4700618982315063</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4072107148002605</v>
+        <v>0.4070479639603379</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.06982646137475967</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4072111557821624</v>
+        <v>0.4070484049422399</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.03733066469430923</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4072105310578013</v>
+        <v>0.4070477802178787</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.09944771230220795</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4072103473153422</v>
+        <v>0.4070475964754196</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.01097082532942295</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4072099430819321</v>
+        <v>0.4070471922420096</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2163528203964233</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4072090978666202</v>
+        <v>0.4070463470266976</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.7672153115272522</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2613603670668531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4072090611181285</v>
+        <v>0.4070463102782059</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.2702710032463074</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.06136036706685302</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4072092081120957</v>
+        <v>0.4070464572721731</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.480827122926712</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4072091346151121</v>
+        <v>0.4070463837751895</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.8661309480667114</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4072092081120957</v>
+        <v>0.4070464572721731</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.1150005310773849</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4072092448605876</v>
+        <v>0.4070464940206651</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.9448679685592651</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4072091346151121</v>
+        <v>0.4070463837751895</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.1386809200048447</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.407209575597014</v>
+        <v>0.4070468247570915</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4817354679107666</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4072094653515385</v>
+        <v>0.4070467145116159</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2150831967592239</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4072094286030466</v>
+        <v>0.407046677763124</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2198289632797241</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4072093551060629</v>
+        <v>0.4070466042661404</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.1380804181098938</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4072093183575712</v>
+        <v>0.4070465675176487</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1249510869383812</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4072090978666202</v>
+        <v>0.4070463470266976</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4223894774913788</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4072090243696366</v>
+        <v>0.407046273529714</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.368375837802887</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4072089508726529</v>
+        <v>0.4070462000327303</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1570782363414764</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4072089876211449</v>
+        <v>0.4070462367812223</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.6761704683303833</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5821290720809754</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4072088773756693</v>
+        <v>0.4070461265357467</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.8924356698989868</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.225618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4072089876211449</v>
+        <v>0.4070462367812223</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
+        <v>0.7251613140106201</v>
+      </c>
+      <c r="JB126" t="n">
         <v>1</v>
       </c>
-      <c r="JB126" t="n">
-        <v>1.225618511228804</v>
-      </c>
       <c r="JC126" t="n">
-        <v>0.4072092816090793</v>
+        <v>0.4070465307691568</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000008.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.5763806700706482</v>
+        <v>0.5763806104660034</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.02000000000000024</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.2251435965299606</v>
+        <v>0.2251436114311218</v>
       </c>
       <c r="JB17" t="n">
         <v>0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.3669618964195251</v>
+        <v>0.3669618666172028</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.271839439868927</v>
+        <v>0.2718394696712494</v>
       </c>
       <c r="JB26" t="n">
         <v>0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.5819368362426758</v>
+        <v>0.5819369554519653</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.3473937511444092</v>
+        <v>0.3473937809467316</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.7639381885528564</v>
+        <v>0.7639381289482117</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.7350853681564331</v>
+        <v>0.7350854277610779</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.5680809617042542</v>
+        <v>0.5680809020996094</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.7437095046043396</v>
+        <v>0.7437094449996948</v>
       </c>
       <c r="JB53" t="n">
         <v>0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.6065155267715454</v>
+        <v>0.6065154671669006</v>
       </c>
       <c r="JB55" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.7493987679481506</v>
+        <v>0.7493988275527954</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.9410029053688049</v>
+        <v>0.9410027861595154</v>
       </c>
       <c r="JB59" t="n">
         <v>0.5799999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.1083724573254585</v>
+        <v>0.1083724349737167</v>
       </c>
       <c r="JB60" t="n">
         <v>0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.2057590484619141</v>
+        <v>0.2057590931653976</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1600000000000001</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.6065806150436401</v>
+        <v>0.6065805554389954</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2007837444543839</v>
+        <v>0.2007837891578674</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.09500638395547867</v>
+        <v>0.09500640630722046</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4526973068714142</v>
+        <v>0.452697366476059</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.9582897424697876</v>
+        <v>0.9582896828651428</v>
       </c>
       <c r="JB88" t="n">
         <v>0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.001253647729754448</v>
+        <v>0.001253649592399597</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.02291245944797993</v>
+        <v>0.02291247062385082</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06978026777505875</v>
+        <v>0.06978028267621994</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.06911052763462067</v>
+        <v>0.06911054998636246</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.6126617789268494</v>
+        <v>0.6126618385314941</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.3948512375354767</v>
+        <v>0.3948512673377991</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.5269074440002441</v>
+        <v>0.5269075036048889</v>
       </c>
       <c r="JB98" t="n">
         <v>0.1600000000000001</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.06982646137475967</v>
+        <v>0.06982649117708206</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.03733066469430923</v>
+        <v>0.03733068332076073</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.09944771230220795</v>
+        <v>0.09944773465394974</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.01097082532942295</v>
+        <v>0.01097083371132612</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.2163528203964233</v>
+        <v>0.2163528352975845</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4817354679107666</v>
+        <v>0.4817355871200562</v>
       </c>
       <c r="JB116" t="n">
         <v>0.1600000000000001</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2150831967592239</v>
+        <v>0.2150831818580627</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.2198289632797241</v>
+        <v>0.2198289781808853</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.6761704683303833</v>
+        <v>0.6761705279350281</v>
       </c>
       <c r="JB124" t="n">
         <v>0.7199999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.7251613140106201</v>
+        <v>0.7251613736152649</v>
       </c>
       <c r="JB126" t="n">
         <v>1</v>
